--- a/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
+++ b/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
@@ -522,6 +522,831 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Pass YDs</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Rush YDs</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Rec YDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>TDs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Sacks</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Flag Pulls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Adam Elmosa</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>WR/S</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dean Elmosa</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WR/DL</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Mohamed Abdelhafez</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Dean Sabah</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Ameer Zhour</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>OL/C</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Gregory Hoard</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WR/DL</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Khaled Salah</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WR/CB</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Othman Othman</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WR/S</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Abed Salah</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Housam Abdallah</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Ammar Zorub</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>TE/DL</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Naseem Elmosa</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ibrahim Kishta</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Abdallah Qasem</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WR/S</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Gillz</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Anthony Jordan</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Yazen Abuzir</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Daniel Elmosa</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Michael Johnson</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WR/DL</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -597,16 +1422,16 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Adam Elmosa</t>
+          <t>Imran Sabir</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
@@ -636,16 +1461,16 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Dean Elmosa</t>
+          <t>Jason Nako</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>WR/DL</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -675,16 +1500,16 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Abdelhafez</t>
+          <t>Zaid Mohammed</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -714,16 +1539,16 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Dean Sabah</t>
+          <t>Amer Wazwaz</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>C/TE</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
@@ -753,16 +1578,16 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Ameer Zhour</t>
+          <t>Ahmad Kiswani</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>OL/C</t>
+          <t>OL/DL/LB</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -792,16 +1617,16 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Gregory Hoard</t>
+          <t>Samer Oda</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>WR/DL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -831,16 +1656,16 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Khaled Salah</t>
+          <t>Sheryaar Khan</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>WR/CB</t>
+          <t>WR/CB/LB</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -870,16 +1695,16 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Othman Othman</t>
+          <t>Ali Hakawati</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -909,16 +1734,16 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Abed Salah</t>
+          <t>Armaan Ghouse</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>WR/DB</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -952,792 +1777,6 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Housam Abdallah</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Ammar Zorub</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>TE/DL</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Naseem Elmosa</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ibrahim Kishta</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>DL</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Abdallah Qasem</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>WR/S</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Gillz</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>OC</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Anthony Jordan</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Yazen Abuzir</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>DL</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Daniel Elmosa</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>POS</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Pass YDs</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Rush YDs</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>REC</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Rec YDs</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>TDs</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Sacks</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Flag Pulls</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Imran Sabir</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Jason Nako</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Zaid Mohammed</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Amer Wazwaz</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>C/TE</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Ahmad Kiswani</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL/LB</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Samer Oda</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Sheryaar Khan</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>WR/CB/LB</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Ali Hakawati</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Armaan Ghouse</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>WR/DB</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
           <t>Kiwi Alsalahi</t>
         </is>
       </c>
@@ -1933,7 +1972,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mostafa El-leboudi</t>
+          <t>Mostafa El-Leboudi</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1963,6 +2002,123 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Shafiq Said</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>WR/DB</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Ashkar</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Osama Alowaid</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WR/DL</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
+++ b/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
@@ -522,20 +522,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,40 +562,70 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Pass Comp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Pass Att</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Pass YDs</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Pass TDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Rush Att</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Rush YDs</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Def INTs</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PBU</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -633,6 +669,24 @@
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -672,6 +726,24 @@
       <c r="K3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -711,6 +783,24 @@
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -750,6 +840,24 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -789,19 +897,37 @@
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Gregory Hoard</t>
+          <t>Khaled Salah</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>WR/DL</t>
+          <t>WR/CB</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -826,21 +952,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Khaled Salah</t>
+          <t>Othman Othman</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>WR/CB</t>
+          <t>WR/S</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -865,21 +1009,39 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Othman Othman</t>
+          <t>Abed Salah</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -904,21 +1066,39 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Abed Salah</t>
+          <t>Housam Abdallah</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -943,21 +1123,39 @@
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Housam Abdallah</t>
+          <t>Ammar Zorub</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE/DL</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
@@ -982,21 +1180,39 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ammar Zorub</t>
+          <t>Naseem Elmosa</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>TE/DL</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -1021,21 +1237,39 @@
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Naseem Elmosa</t>
+          <t>Ibrahim Kishta</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -1060,21 +1294,39 @@
         <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Ibrahim Kishta</t>
+          <t>Abdallah Qasem</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>WR/S</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -1099,21 +1351,39 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Abdallah Qasem</t>
+          <t>Gillz</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -1138,21 +1408,39 @@
         <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Gillz</t>
+          <t>Anthony Jordan</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -1177,21 +1465,39 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Anthony Jordan</t>
+          <t>Yazen Abuzir</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -1216,21 +1522,39 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Yazen Abuzir</t>
+          <t>Daniel Elmosa</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -1255,21 +1579,39 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Daniel Elmosa</t>
+          <t>Michael Johnson</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>WR/DL</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -1294,21 +1636,39 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Michael Johnson</t>
+          <t>Weezy</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>WR/DL</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
@@ -1333,6 +1693,24 @@
         <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1347,20 +1725,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1381,40 +1765,70 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Pass Comp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Pass Att</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Pass YDs</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Pass TDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Rush Att</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Rush YDs</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Def INTs</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PBU</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1458,6 +1872,24 @@
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1497,6 +1929,24 @@
       <c r="K3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1536,6 +1986,24 @@
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1575,6 +2043,24 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1614,6 +2100,24 @@
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1653,6 +2157,24 @@
       <c r="K7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1692,6 +2214,24 @@
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1731,6 +2271,24 @@
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1770,6 +2328,24 @@
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1809,6 +2385,24 @@
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1848,6 +2442,24 @@
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1887,6 +2499,24 @@
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1924,6 +2554,24 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1965,6 +2613,24 @@
       <c r="K15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2004,6 +2670,24 @@
       <c r="K16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2043,6 +2727,24 @@
       <c r="K17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2082,6 +2784,24 @@
       <c r="K18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2119,6 +2839,24 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
+++ b/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -46,8 +46,13 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +71,14 @@
         <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border/>
     <border>
       <left style="thin">
@@ -108,11 +119,17 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -153,6 +170,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1506,13 +1529,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
     <col width="22" customWidth="1" style="17" min="2" max="2"/>
     <col width="14" customWidth="1" style="17" min="3" max="3"/>
     <col width="11" customWidth="1" style="17" min="4" max="18"/>
+    <col width="10" customWidth="1" style="17" min="16" max="16"/>
     <col width="8.710000000000001" customWidth="1" style="17" min="19" max="27"/>
   </cols>
   <sheetData>
@@ -1592,17 +1616,22 @@
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
+        <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1656,13 +1685,16 @@
       <c r="O2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="13" t="n">
+      <c r="P2" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1714,13 +1746,16 @@
       <c r="O3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="13" t="n">
+      <c r="P3" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="13" t="n">
+      <c r="S3" s="13" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1772,13 +1807,16 @@
       <c r="O4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="13" t="n">
+      <c r="P4" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1830,13 +1868,16 @@
       <c r="O5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1888,13 +1929,16 @@
       <c r="O6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1946,13 +1990,16 @@
       <c r="O7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2004,13 +2051,16 @@
       <c r="O8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2062,13 +2112,16 @@
       <c r="O9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="13" t="n">
+      <c r="P9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2120,13 +2173,16 @@
       <c r="O10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2178,13 +2234,16 @@
       <c r="O11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="13" t="n">
+      <c r="P11" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2236,13 +2295,16 @@
       <c r="O12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2294,13 +2356,16 @@
       <c r="O13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="13" t="n">
+      <c r="P13" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2350,9 +2415,9 @@
         <v>0</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
@@ -2361,7 +2426,10 @@
       <c r="R14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="S14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>2pt def TD</t>
         </is>
@@ -2415,13 +2483,16 @@
       <c r="O15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2473,13 +2544,16 @@
       <c r="O16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="13" t="n">
+      <c r="P16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2531,13 +2605,16 @@
       <c r="O17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="13" t="n">
+      <c r="P17" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2589,13 +2666,16 @@
       <c r="O18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="13" t="n">
+      <c r="P18" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2647,13 +2727,16 @@
       <c r="O19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="13" t="n">
+      <c r="P19" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2705,16 +2788,19 @@
       <c r="O20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="13" t="n">
+      <c r="P20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>2pt def TD</t>
         </is>
@@ -2764,13 +2850,13 @@
       <c r="O21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3765,13 +3851,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
     <col width="22" customWidth="1" style="17" min="2" max="2"/>
     <col width="14" customWidth="1" style="17" min="3" max="3"/>
     <col width="11" customWidth="1" style="17" min="4" max="18"/>
+    <col width="10" customWidth="1" style="17" min="16" max="16"/>
     <col width="8.710000000000001" customWidth="1" style="17" min="19" max="27"/>
   </cols>
   <sheetData>
@@ -3851,17 +3938,22 @@
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
+        <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -3915,13 +4007,16 @@
       <c r="O2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="13" t="n">
+      <c r="P2" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3973,13 +4068,16 @@
       <c r="O3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="13" t="n">
+      <c r="P3" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q3" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4031,13 +4129,16 @@
       <c r="O4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="13" t="n">
+      <c r="P4" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="R4" s="13" t="n">
+      <c r="S4" s="13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4089,13 +4190,16 @@
       <c r="O5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4147,13 +4251,16 @@
       <c r="O6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4205,13 +4312,16 @@
       <c r="O7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4263,13 +4373,16 @@
       <c r="O8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4321,13 +4434,16 @@
       <c r="O9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="13" t="n">
+      <c r="P9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4379,13 +4495,16 @@
       <c r="O10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4437,16 +4556,19 @@
       <c r="O11" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="P11" s="13" t="n">
-        <v>0</v>
+      <c r="P11" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="Q11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>pick6</t>
         </is>
@@ -4500,13 +4622,16 @@
       <c r="O12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4558,13 +4683,16 @@
       <c r="O13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="13" t="n">
+      <c r="P13" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4616,13 +4744,16 @@
       <c r="O14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="13" t="n">
+      <c r="P14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4674,13 +4805,16 @@
       <c r="O15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4732,13 +4866,16 @@
       <c r="O16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="13" t="n">
+      <c r="P16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4790,13 +4927,16 @@
       <c r="O17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="13" t="n">
+      <c r="P17" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4848,13 +4988,16 @@
       <c r="O18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="13" t="n">
+      <c r="P18" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="R18" s="13" t="n">
+      <c r="S18" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4906,13 +5049,16 @@
       <c r="O19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="13" t="n">
+      <c r="P19" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="R19" s="13" t="n">
+      <c r="S19" s="13" t="n">
         <v>2</v>
       </c>
     </row>

--- a/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
+++ b/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
@@ -4551,7 +4551,7 @@
         <v>15</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="15" t="n">
         <v>1</v>
@@ -4678,7 +4678,7 @@
         <v>43</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>0</v>

--- a/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
+++ b/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" s="13" t="n">
         <v>2</v>

--- a/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
+++ b/game-stats/Week2_LOB_vs_Desert-Lions.xlsx
@@ -2810,7 +2810,11 @@
       <c r="A21" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Charles II</t>
+        </is>
+      </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
           <t>WR</t>
